--- a/events/Pau_2016_WC/Pau_2016_WC_start.xlsx
+++ b/events/Pau_2016_WC/Pau_2016_WC_start.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W661"/>
+  <dimension ref="A1:AC661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,17 +519,47 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Name4</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Name5</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Name6</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>ICF_ID1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ICF_ID2</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ICF_ID3</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ICF_ID4</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ICF_ID5</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ICF_ID6</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1413,7 @@
           <t>ZISEKAS Panagiotis</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>64786</t>
         </is>
@@ -1441,7 +1471,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -1499,7 +1529,7 @@
           <t>POMEROY Spencer</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>57783</t>
         </is>
@@ -1557,7 +1587,7 @@
           <t>SEEMANN Eloi</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>44378</t>
         </is>
@@ -1615,7 +1645,7 @@
           <t>BRE Charles</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>68753</t>
         </is>
@@ -1673,7 +1703,7 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -1731,7 +1761,7 @@
           <t>PLEWA Przemyslaw</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>35950</t>
         </is>
@@ -1789,7 +1819,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -1847,7 +1877,7 @@
           <t>SMITH Tyler</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>51904</t>
         </is>
@@ -1905,7 +1935,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -1963,7 +1993,7 @@
           <t>CONTRERAS Sebastian</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>36926</t>
         </is>
@@ -2021,7 +2051,7 @@
           <t>CHOOAMPAI Rattanajet</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>51801</t>
         </is>
@@ -2079,7 +2109,7 @@
           <t>CARTER Tristan</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>51890</t>
         </is>
@@ -2137,7 +2167,7 @@
           <t>COF Blaz</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>36897</t>
         </is>
@@ -2195,7 +2225,7 @@
           <t>SOSA Angelo</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>51793</t>
         </is>
@@ -2239,7 +2269,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>LIB</t>
+          <t>LBN</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -2253,6 +2283,11 @@
           <t>MERJAN Richard</t>
         </is>
       </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>45918</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2306,7 +2341,7 @@
           <t>LIU Chin-Han</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>51894</t>
         </is>
@@ -2364,7 +2399,7 @@
           <t>CHAIDET Yutthakan</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>51798</t>
         </is>
@@ -2422,7 +2457,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -2480,7 +2515,7 @@
           <t>WASHER Patrick</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>42081</t>
         </is>
@@ -2538,7 +2573,7 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -2596,7 +2631,7 @@
           <t>FERNANDEZ Luis</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>51851</t>
         </is>
@@ -2654,7 +2689,7 @@
           <t>CORREA Charles</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
@@ -2712,7 +2747,7 @@
           <t>TIMAKOV Dmitriy</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>53527</t>
         </is>
@@ -2770,7 +2805,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -2828,7 +2863,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -2886,7 +2921,7 @@
           <t>CURCEL Leonardo</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
@@ -2944,7 +2979,7 @@
           <t>SZTUBA Igor</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>35087</t>
         </is>
@@ -3055,7 +3090,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -3113,7 +3148,7 @@
           <t>MIRGORODSKY Marko</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>42019</t>
         </is>
@@ -3171,7 +3206,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -3229,7 +3264,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -3287,7 +3322,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -3345,7 +3380,7 @@
           <t>ERGUIN Jon</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>35740</t>
         </is>
@@ -3403,7 +3438,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -3461,7 +3496,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -3572,7 +3607,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -3630,7 +3665,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -3688,7 +3723,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -3746,7 +3781,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -3804,7 +3839,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -3862,7 +3897,7 @@
           <t>BREUER Florian</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>39171</t>
         </is>
@@ -3920,7 +3955,7 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -4031,7 +4066,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -4089,7 +4124,7 @@
           <t>PESCHIER Nicolas</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>35401</t>
         </is>
@@ -4147,7 +4182,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -4205,7 +4240,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -4263,7 +4298,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -4321,7 +4356,7 @@
           <t>TILLARD Pierre-Antoine</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
@@ -4379,7 +4414,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -4437,7 +4472,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -4495,7 +4530,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -4553,7 +4588,7 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -4611,7 +4646,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -4669,7 +4704,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -4727,7 +4762,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -4785,7 +4820,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -4843,7 +4878,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -4901,7 +4936,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -4959,7 +4994,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -5017,7 +5052,7 @@
           <t>CHUNG Yu-Han</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>51895</t>
         </is>
@@ -5075,7 +5110,7 @@
           <t>DONNELLY Sage</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>60119</t>
         </is>
@@ -5133,7 +5168,7 @@
           <t>CHEN Wei-Han</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>61630</t>
         </is>
@@ -5191,7 +5226,7 @@
           <t>NAVEAU Laurine</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>53246</t>
         </is>
@@ -5249,7 +5284,7 @@
           <t>DUANGLAWA Atcharaporn</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>61799</t>
         </is>
@@ -5307,7 +5342,7 @@
           <t>GLEJTEKOVA Simona</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>55166</t>
         </is>
@@ -5365,7 +5400,7 @@
           <t>SKACHOVA Monika</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>53078</t>
         </is>
@@ -5423,7 +5458,7 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -5534,7 +5569,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -5592,7 +5627,7 @@
           <t>TRAVERS Kelly</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>51643</t>
         </is>
@@ -5650,7 +5685,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -5761,7 +5796,7 @@
           <t>SATKOVA Martina</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>42008</t>
         </is>
@@ -5819,7 +5854,7 @@
           <t>BIZJAK Nina</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>39984</t>
         </is>
@@ -5877,7 +5912,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -5935,7 +5970,7 @@
           <t>RANKIN Georgia</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>38435</t>
         </is>
@@ -5993,7 +6028,7 @@
           <t>JANCZY Justyna</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>43975</t>
         </is>
@@ -6051,7 +6086,7 @@
           <t>MATULKOVA Jana</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>37274</t>
         </is>
@@ -6109,7 +6144,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -6220,7 +6255,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -6278,7 +6313,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -6336,7 +6371,7 @@
           <t>BORROWS Alison</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="X104" t="inlineStr">
         <is>
           <t>38440</t>
         </is>
@@ -6394,7 +6429,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -6452,7 +6487,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -6563,7 +6598,7 @@
           <t>GIBSON Eilidh</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
+      <c r="X108" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
@@ -6621,7 +6656,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -6732,7 +6767,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
+      <c r="X111" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -6790,7 +6825,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr">
+      <c r="X112" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -6901,7 +6936,7 @@
           <t>TEAGUE Eoin</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
+      <c r="X114" t="inlineStr">
         <is>
           <t>37913</t>
         </is>
@@ -6959,7 +6994,7 @@
           <t>SOUDI Mathis</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
+      <c r="X115" t="inlineStr">
         <is>
           <t>69447</t>
         </is>
@@ -7017,7 +7052,7 @@
           <t>ZISEKAS Panagiotis</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="X116" t="inlineStr">
         <is>
           <t>64786</t>
         </is>
@@ -7075,7 +7110,7 @@
           <t>RACZ Koppany</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
+      <c r="X117" t="inlineStr">
         <is>
           <t>69570</t>
         </is>
@@ -7133,7 +7168,7 @@
           <t>REINOSO DIAZ Antonio</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
+      <c r="X118" t="inlineStr">
         <is>
           <t>70420</t>
         </is>
@@ -7191,7 +7226,7 @@
           <t>WELLS Cameron</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
+      <c r="X119" t="inlineStr">
         <is>
           <t>58134</t>
         </is>
@@ -7249,7 +7284,7 @@
           <t>NGAMSANGA Paitas</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="X120" t="inlineStr">
         <is>
           <t>68857</t>
         </is>
@@ -7307,7 +7342,7 @@
           <t>BAK Jaehyeong</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
+      <c r="X121" t="inlineStr">
         <is>
           <t>66073</t>
         </is>
@@ -7365,7 +7400,7 @@
           <t>SOARES Renan</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>42776</t>
         </is>
@@ -7423,7 +7458,7 @@
           <t>YAZAWA Kazuki</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
+      <c r="X123" t="inlineStr">
         <is>
           <t>36482</t>
         </is>
@@ -7481,7 +7516,7 @@
           <t>MENDEZ Luis</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
+      <c r="X124" t="inlineStr">
         <is>
           <t>41635</t>
         </is>
@@ -7539,7 +7574,7 @@
           <t>TRAVOSTINO Benjamin</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
+      <c r="X125" t="inlineStr">
         <is>
           <t>68795</t>
         </is>
@@ -7650,7 +7685,7 @@
           <t>NIKOLOVSKI Atanas</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
+      <c r="X127" t="inlineStr">
         <is>
           <t>35582</t>
         </is>
@@ -7708,7 +7743,7 @@
           <t>LEE EDWARDS Ciaran</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
+      <c r="X128" t="inlineStr">
         <is>
           <t>35614</t>
         </is>
@@ -7766,7 +7801,7 @@
           <t>SWETNAM Huw</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr">
+      <c r="X129" t="inlineStr">
         <is>
           <t>35652</t>
         </is>
@@ -7824,7 +7859,7 @@
           <t>DRAPER Warwick</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
+      <c r="X130" t="inlineStr">
         <is>
           <t>36536</t>
         </is>
@@ -7882,7 +7917,7 @@
           <t>WESTFALL Tyler</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="X131" t="inlineStr">
         <is>
           <t>51919</t>
         </is>
@@ -7940,7 +7975,7 @@
           <t>MAPELLI Guilherme Marcello</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
+      <c r="X132" t="inlineStr">
         <is>
           <t>38015</t>
         </is>
@@ -7998,7 +8033,7 @@
           <t>OGURA Takashi</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
+      <c r="X133" t="inlineStr">
         <is>
           <t>37679</t>
         </is>
@@ -8056,7 +8091,7 @@
           <t>STANOVSKY Martin</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
+      <c r="X134" t="inlineStr">
         <is>
           <t>68782</t>
         </is>
@@ -8114,7 +8149,7 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
+      <c r="X135" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -8172,7 +8207,7 @@
           <t>ECHEVERRIA OLGUIN Andraz</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
+      <c r="X136" t="inlineStr">
         <is>
           <t>41646</t>
         </is>
@@ -8230,7 +8265,7 @@
           <t>GASSOU Mel</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
+      <c r="X137" t="inlineStr">
         <is>
           <t>35598</t>
         </is>
@@ -8288,7 +8323,7 @@
           <t>TUIRAVIRAVI Daniel</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
+      <c r="X138" t="inlineStr">
         <is>
           <t>51998</t>
         </is>
@@ -8346,7 +8381,7 @@
           <t>CESPEDES PEREZ Arnaldo</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
+      <c r="X139" t="inlineStr">
         <is>
           <t>41634</t>
         </is>
@@ -8404,7 +8439,7 @@
           <t>DAVIDSON Elliott</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="X140" t="inlineStr">
         <is>
           <t>43077</t>
         </is>
@@ -8462,7 +8497,7 @@
           <t>CORTEZ Geronimo</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
+      <c r="X141" t="inlineStr">
         <is>
           <t>51835</t>
         </is>
@@ -8520,7 +8555,7 @@
           <t>HELLARD Suworna</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
+      <c r="X142" t="inlineStr">
         <is>
           <t>43088</t>
         </is>
@@ -8578,7 +8613,7 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
+      <c r="X143" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -8636,7 +8671,7 @@
           <t>PEREZ Alexis</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
+      <c r="X144" t="inlineStr">
         <is>
           <t>41649</t>
         </is>
@@ -8694,7 +8729,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
+      <c r="X145" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -8752,7 +8787,7 @@
           <t>MARTINS TAQUES Ricardo</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr">
+      <c r="X146" t="inlineStr">
         <is>
           <t>38022</t>
         </is>
@@ -8810,7 +8845,7 @@
           <t>YOSHIDA Taku</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr">
+      <c r="X147" t="inlineStr">
         <is>
           <t>41611</t>
         </is>
@@ -8868,7 +8903,7 @@
           <t>MUNSCH Manuel</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
+      <c r="X148" t="inlineStr">
         <is>
           <t>35631</t>
         </is>
@@ -8926,7 +8961,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
+      <c r="X149" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -8984,7 +9019,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
+      <c r="X150" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -9042,7 +9077,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
+      <c r="X151" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -9100,7 +9135,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
+      <c r="X152" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -9158,7 +9193,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
+      <c r="X153" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -9216,7 +9251,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
+      <c r="X154" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -9274,7 +9309,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
+      <c r="X155" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -9332,7 +9367,7 @@
           <t>NABASKUES Unai</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
+      <c r="X156" t="inlineStr">
         <is>
           <t>38775</t>
         </is>
@@ -9390,7 +9425,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
+      <c r="X157" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -9501,7 +9536,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
+      <c r="X159" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -9559,7 +9594,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
+      <c r="X160" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -9617,7 +9652,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr">
+      <c r="X161" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -9675,7 +9710,7 @@
           <t>POWELL Richard</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
+      <c r="X162" t="inlineStr">
         <is>
           <t>36444</t>
         </is>
@@ -9786,7 +9821,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
+      <c r="X164" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -9844,7 +9879,7 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr">
+      <c r="X165" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -9955,7 +9990,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
+      <c r="X167" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -10013,7 +10048,7 @@
           <t>BOECKELMANN Paul</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
+      <c r="X168" t="inlineStr">
         <is>
           <t>35118</t>
         </is>
@@ -10071,7 +10106,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr">
+      <c r="X169" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -10129,7 +10164,7 @@
           <t>DAILLE Etienne</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
+      <c r="X170" t="inlineStr">
         <is>
           <t>35308</t>
         </is>
@@ -10187,7 +10222,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
+      <c r="X171" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -10245,7 +10280,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
+      <c r="X172" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -10303,7 +10338,7 @@
           <t>MEGLIC Jure</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
+      <c r="X173" t="inlineStr">
         <is>
           <t>35590</t>
         </is>
@@ -10361,7 +10396,7 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
+      <c r="X174" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -10419,7 +10454,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
+      <c r="X175" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -10477,7 +10512,7 @@
           <t>HILGERT Lubos</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
+      <c r="X176" t="inlineStr">
         <is>
           <t>35032</t>
         </is>
@@ -10535,7 +10570,7 @@
           <t>ALBREHT Martin</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
+      <c r="X177" t="inlineStr">
         <is>
           <t>36898</t>
         </is>
@@ -10593,7 +10628,7 @@
           <t>PETERLIN Janos</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
+      <c r="X178" t="inlineStr">
         <is>
           <t>36268</t>
         </is>
@@ -10651,7 +10686,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
+      <c r="X179" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -10709,7 +10744,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
+      <c r="X180" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -10767,7 +10802,7 @@
           <t>ROMEO Andrea</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr">
+      <c r="X181" t="inlineStr">
         <is>
           <t>35502</t>
         </is>
@@ -10825,7 +10860,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
+      <c r="X182" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -10883,7 +10918,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U183" t="inlineStr">
+      <c r="X183" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -10941,7 +10976,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
+      <c r="X184" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -10999,7 +11034,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
+      <c r="X185" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -11057,7 +11092,7 @@
           <t>MOLMENTI Daniele</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
+      <c r="X186" t="inlineStr">
         <is>
           <t>42017</t>
         </is>
@@ -11115,7 +11150,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
+      <c r="X187" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -11173,7 +11208,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
+      <c r="X188" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -11231,7 +11266,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U189" t="inlineStr">
+      <c r="X189" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -11289,7 +11324,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
+      <c r="X190" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -11347,7 +11382,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
+      <c r="X191" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -11405,7 +11440,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr">
+      <c r="X192" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -11463,7 +11498,7 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
+      <c r="X193" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -11521,7 +11556,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
+      <c r="X194" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -11579,7 +11614,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
+      <c r="X195" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -11637,7 +11672,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
+      <c r="X196" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -11695,7 +11730,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr">
+      <c r="X197" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -11753,7 +11788,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
+      <c r="X198" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -11811,7 +11846,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
+      <c r="X199" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -11869,7 +11904,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
+      <c r="X200" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -11927,7 +11962,7 @@
           <t>ZISEKAS Panagiotis</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr">
+      <c r="X201" t="inlineStr">
         <is>
           <t>64786</t>
         </is>
@@ -11985,7 +12020,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
+      <c r="X202" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -12043,7 +12078,7 @@
           <t>POMEROY Spencer</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
+      <c r="X203" t="inlineStr">
         <is>
           <t>57783</t>
         </is>
@@ -12101,7 +12136,7 @@
           <t>SEEMANN Eloi</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
+      <c r="X204" t="inlineStr">
         <is>
           <t>44378</t>
         </is>
@@ -12159,7 +12194,7 @@
           <t>BRE Charles</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr">
+      <c r="X205" t="inlineStr">
         <is>
           <t>68753</t>
         </is>
@@ -12217,7 +12252,7 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U206" t="inlineStr">
+      <c r="X206" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -12275,7 +12310,7 @@
           <t>PLEWA Przemyslaw</t>
         </is>
       </c>
-      <c r="U207" t="inlineStr">
+      <c r="X207" t="inlineStr">
         <is>
           <t>35950</t>
         </is>
@@ -12333,7 +12368,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U208" t="inlineStr">
+      <c r="X208" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -12391,7 +12426,7 @@
           <t>SMITH Tyler</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr">
+      <c r="X209" t="inlineStr">
         <is>
           <t>51904</t>
         </is>
@@ -12449,7 +12484,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr">
+      <c r="X210" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -12507,7 +12542,7 @@
           <t>CONTRERAS Sebastian</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
+      <c r="X211" t="inlineStr">
         <is>
           <t>36926</t>
         </is>
@@ -12565,7 +12600,7 @@
           <t>CHOOAMPAI Rattanajet</t>
         </is>
       </c>
-      <c r="U212" t="inlineStr">
+      <c r="X212" t="inlineStr">
         <is>
           <t>51801</t>
         </is>
@@ -12623,7 +12658,7 @@
           <t>CARTER Tristan</t>
         </is>
       </c>
-      <c r="U213" t="inlineStr">
+      <c r="X213" t="inlineStr">
         <is>
           <t>51890</t>
         </is>
@@ -12681,7 +12716,7 @@
           <t>COF Blaz</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr">
+      <c r="X214" t="inlineStr">
         <is>
           <t>36897</t>
         </is>
@@ -12739,7 +12774,7 @@
           <t>SOSA Angelo</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
+      <c r="X215" t="inlineStr">
         <is>
           <t>51793</t>
         </is>
@@ -12783,7 +12818,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>LIB</t>
+          <t>LBN</t>
         </is>
       </c>
       <c r="J216" t="n">
@@ -12797,6 +12832,11 @@
           <t>MERJAN Richard</t>
         </is>
       </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>45918</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -12850,7 +12890,7 @@
           <t>LIU Chin-Han</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
+      <c r="X217" t="inlineStr">
         <is>
           <t>51894</t>
         </is>
@@ -12908,7 +12948,7 @@
           <t>CHAIDET Yutthakan</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr">
+      <c r="X218" t="inlineStr">
         <is>
           <t>51798</t>
         </is>
@@ -12966,7 +13006,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U219" t="inlineStr">
+      <c r="X219" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -13024,7 +13064,7 @@
           <t>WASHER Patrick</t>
         </is>
       </c>
-      <c r="U220" t="inlineStr">
+      <c r="X220" t="inlineStr">
         <is>
           <t>42081</t>
         </is>
@@ -13082,7 +13122,7 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
+      <c r="X221" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -13140,7 +13180,7 @@
           <t>FERNANDEZ Luis</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
+      <c r="X222" t="inlineStr">
         <is>
           <t>51851</t>
         </is>
@@ -13198,7 +13238,7 @@
           <t>CORREA Charles</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
+      <c r="X223" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
@@ -13256,7 +13296,7 @@
           <t>TIMAKOV Dmitriy</t>
         </is>
       </c>
-      <c r="U224" t="inlineStr">
+      <c r="X224" t="inlineStr">
         <is>
           <t>53527</t>
         </is>
@@ -13314,7 +13354,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U225" t="inlineStr">
+      <c r="X225" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -13372,7 +13412,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
+      <c r="X226" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -13430,7 +13470,7 @@
           <t>CURCEL Leonardo</t>
         </is>
       </c>
-      <c r="U227" t="inlineStr">
+      <c r="X227" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
@@ -13488,7 +13528,7 @@
           <t>SZTUBA Igor</t>
         </is>
       </c>
-      <c r="U228" t="inlineStr">
+      <c r="X228" t="inlineStr">
         <is>
           <t>35087</t>
         </is>
@@ -13599,7 +13639,7 @@
           <t>MIRGORODSKY Marko</t>
         </is>
       </c>
-      <c r="U230" t="inlineStr">
+      <c r="X230" t="inlineStr">
         <is>
           <t>42019</t>
         </is>
@@ -13657,7 +13697,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U231" t="inlineStr">
+      <c r="X231" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -13715,7 +13755,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U232" t="inlineStr">
+      <c r="X232" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -13773,7 +13813,7 @@
           <t>ERGUIN Jon</t>
         </is>
       </c>
-      <c r="U233" t="inlineStr">
+      <c r="X233" t="inlineStr">
         <is>
           <t>35740</t>
         </is>
@@ -13884,7 +13924,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
+      <c r="X235" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -13942,7 +13982,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U236" t="inlineStr">
+      <c r="X236" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -14000,7 +14040,7 @@
           <t>BREUER Florian</t>
         </is>
       </c>
-      <c r="U237" t="inlineStr">
+      <c r="X237" t="inlineStr">
         <is>
           <t>39171</t>
         </is>
@@ -14111,7 +14151,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U239" t="inlineStr">
+      <c r="X239" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -14169,7 +14209,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
+      <c r="X240" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -14227,7 +14267,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
+      <c r="X241" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -14285,7 +14325,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
+      <c r="X242" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -14343,7 +14383,7 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
+      <c r="X243" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -14401,7 +14441,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U244" t="inlineStr">
+      <c r="X244" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -14459,7 +14499,7 @@
           <t>CHUNG Yu-Han</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>51895</t>
         </is>
@@ -14517,7 +14557,7 @@
           <t>DONNELLY Sage</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
+      <c r="X246" t="inlineStr">
         <is>
           <t>60119</t>
         </is>
@@ -14575,7 +14615,7 @@
           <t>CHEN Wei-Han</t>
         </is>
       </c>
-      <c r="U247" t="inlineStr">
+      <c r="X247" t="inlineStr">
         <is>
           <t>61630</t>
         </is>
@@ -14633,7 +14673,7 @@
           <t>DUANGLAWA Atcharaporn</t>
         </is>
       </c>
-      <c r="U248" t="inlineStr">
+      <c r="X248" t="inlineStr">
         <is>
           <t>61799</t>
         </is>
@@ -14691,7 +14731,7 @@
           <t>GLEJTEKOVA Simona</t>
         </is>
       </c>
-      <c r="U249" t="inlineStr">
+      <c r="X249" t="inlineStr">
         <is>
           <t>55166</t>
         </is>
@@ -14749,7 +14789,7 @@
           <t>SKACHOVA Monika</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
+      <c r="X250" t="inlineStr">
         <is>
           <t>53078</t>
         </is>
@@ -14807,7 +14847,7 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U251" t="inlineStr">
+      <c r="X251" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -14918,7 +14958,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U253" t="inlineStr">
+      <c r="X253" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -14976,7 +15016,7 @@
           <t>TRAVERS Kelly</t>
         </is>
       </c>
-      <c r="U254" t="inlineStr">
+      <c r="X254" t="inlineStr">
         <is>
           <t>51643</t>
         </is>
@@ -15034,7 +15074,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U255" t="inlineStr">
+      <c r="X255" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -15145,7 +15185,7 @@
           <t>BIZJAK Nina</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr">
+      <c r="X257" t="inlineStr">
         <is>
           <t>39984</t>
         </is>
@@ -15203,7 +15243,7 @@
           <t>RANKIN Georgia</t>
         </is>
       </c>
-      <c r="U258" t="inlineStr">
+      <c r="X258" t="inlineStr">
         <is>
           <t>38435</t>
         </is>
@@ -15261,7 +15301,7 @@
           <t>JANCZY Justyna</t>
         </is>
       </c>
-      <c r="U259" t="inlineStr">
+      <c r="X259" t="inlineStr">
         <is>
           <t>43975</t>
         </is>
@@ -15319,7 +15359,7 @@
           <t>MATULKOVA Jana</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
+      <c r="X260" t="inlineStr">
         <is>
           <t>37274</t>
         </is>
@@ -15377,7 +15417,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U261" t="inlineStr">
+      <c r="X261" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -15435,7 +15475,7 @@
           <t>BORROWS Alison</t>
         </is>
       </c>
-      <c r="U262" t="inlineStr">
+      <c r="X262" t="inlineStr">
         <is>
           <t>38440</t>
         </is>
@@ -15493,7 +15533,7 @@
           <t>TEAGUE Eoin</t>
         </is>
       </c>
-      <c r="U263" t="inlineStr">
+      <c r="X263" t="inlineStr">
         <is>
           <t>37913</t>
         </is>
@@ -15551,7 +15591,7 @@
           <t>SOUDI Mathis</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
+      <c r="X264" t="inlineStr">
         <is>
           <t>69447</t>
         </is>
@@ -15609,7 +15649,7 @@
           <t>ZISEKAS Panagiotis</t>
         </is>
       </c>
-      <c r="U265" t="inlineStr">
+      <c r="X265" t="inlineStr">
         <is>
           <t>64786</t>
         </is>
@@ -15667,7 +15707,7 @@
           <t>RACZ Koppany</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
+      <c r="X266" t="inlineStr">
         <is>
           <t>69570</t>
         </is>
@@ -15725,7 +15765,7 @@
           <t>REINOSO DIAZ Antonio</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr">
+      <c r="X267" t="inlineStr">
         <is>
           <t>70420</t>
         </is>
@@ -15783,7 +15823,7 @@
           <t>WELLS Cameron</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
+      <c r="X268" t="inlineStr">
         <is>
           <t>58134</t>
         </is>
@@ -15841,7 +15881,7 @@
           <t>NGAMSANGA Paitas</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
+      <c r="X269" t="inlineStr">
         <is>
           <t>68857</t>
         </is>
@@ -15899,7 +15939,7 @@
           <t>BAK Jaehyeong</t>
         </is>
       </c>
-      <c r="U270" t="inlineStr">
+      <c r="X270" t="inlineStr">
         <is>
           <t>66073</t>
         </is>
@@ -15957,7 +15997,7 @@
           <t>SOARES Renan</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
+      <c r="X271" t="inlineStr">
         <is>
           <t>42776</t>
         </is>
@@ -16015,7 +16055,7 @@
           <t>YAZAWA Kazuki</t>
         </is>
       </c>
-      <c r="U272" t="inlineStr">
+      <c r="X272" t="inlineStr">
         <is>
           <t>36482</t>
         </is>
@@ -16073,7 +16113,7 @@
           <t>MENDEZ Luis</t>
         </is>
       </c>
-      <c r="U273" t="inlineStr">
+      <c r="X273" t="inlineStr">
         <is>
           <t>41635</t>
         </is>
@@ -16184,7 +16224,7 @@
           <t>NIKOLOVSKI Atanas</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr">
+      <c r="X275" t="inlineStr">
         <is>
           <t>35582</t>
         </is>
@@ -16242,7 +16282,7 @@
           <t>LEE EDWARDS Ciaran</t>
         </is>
       </c>
-      <c r="U276" t="inlineStr">
+      <c r="X276" t="inlineStr">
         <is>
           <t>35614</t>
         </is>
@@ -16300,7 +16340,7 @@
           <t>SWETNAM Huw</t>
         </is>
       </c>
-      <c r="U277" t="inlineStr">
+      <c r="X277" t="inlineStr">
         <is>
           <t>35652</t>
         </is>
@@ -16358,7 +16398,7 @@
           <t>DRAPER Warwick</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr">
+      <c r="X278" t="inlineStr">
         <is>
           <t>36536</t>
         </is>
@@ -16416,7 +16456,7 @@
           <t>WESTFALL Tyler</t>
         </is>
       </c>
-      <c r="U279" t="inlineStr">
+      <c r="X279" t="inlineStr">
         <is>
           <t>51919</t>
         </is>
@@ -16474,7 +16514,7 @@
           <t>MAPELLI Guilherme Marcello</t>
         </is>
       </c>
-      <c r="U280" t="inlineStr">
+      <c r="X280" t="inlineStr">
         <is>
           <t>38015</t>
         </is>
@@ -16532,7 +16572,7 @@
           <t>OGURA Takashi</t>
         </is>
       </c>
-      <c r="U281" t="inlineStr">
+      <c r="X281" t="inlineStr">
         <is>
           <t>37679</t>
         </is>
@@ -16590,7 +16630,7 @@
           <t>STANOVSKY Martin</t>
         </is>
       </c>
-      <c r="U282" t="inlineStr">
+      <c r="X282" t="inlineStr">
         <is>
           <t>68782</t>
         </is>
@@ -16648,7 +16688,7 @@
           <t>ECHEVERRIA OLGUIN Andraz</t>
         </is>
       </c>
-      <c r="U283" t="inlineStr">
+      <c r="X283" t="inlineStr">
         <is>
           <t>41646</t>
         </is>
@@ -16706,7 +16746,7 @@
           <t>GASSOU Mel</t>
         </is>
       </c>
-      <c r="U284" t="inlineStr">
+      <c r="X284" t="inlineStr">
         <is>
           <t>35598</t>
         </is>
@@ -16764,7 +16804,7 @@
           <t>TUIRAVIRAVI Daniel</t>
         </is>
       </c>
-      <c r="U285" t="inlineStr">
+      <c r="X285" t="inlineStr">
         <is>
           <t>51998</t>
         </is>
@@ -16822,7 +16862,7 @@
           <t>CESPEDES PEREZ Arnaldo</t>
         </is>
       </c>
-      <c r="U286" t="inlineStr">
+      <c r="X286" t="inlineStr">
         <is>
           <t>41634</t>
         </is>
@@ -16880,7 +16920,7 @@
           <t>DAVIDSON Elliott</t>
         </is>
       </c>
-      <c r="U287" t="inlineStr">
+      <c r="X287" t="inlineStr">
         <is>
           <t>43077</t>
         </is>
@@ -16938,7 +16978,7 @@
           <t>CORTEZ Geronimo</t>
         </is>
       </c>
-      <c r="U288" t="inlineStr">
+      <c r="X288" t="inlineStr">
         <is>
           <t>51835</t>
         </is>
@@ -16996,7 +17036,7 @@
           <t>HELLARD Suworna</t>
         </is>
       </c>
-      <c r="U289" t="inlineStr">
+      <c r="X289" t="inlineStr">
         <is>
           <t>43088</t>
         </is>
@@ -17054,7 +17094,7 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U290" t="inlineStr">
+      <c r="X290" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -17112,7 +17152,7 @@
           <t>PEREZ Alexis</t>
         </is>
       </c>
-      <c r="U291" t="inlineStr">
+      <c r="X291" t="inlineStr">
         <is>
           <t>41649</t>
         </is>
@@ -17170,7 +17210,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U292" t="inlineStr">
+      <c r="X292" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -17228,7 +17268,7 @@
           <t>MARTINS TAQUES Ricardo</t>
         </is>
       </c>
-      <c r="U293" t="inlineStr">
+      <c r="X293" t="inlineStr">
         <is>
           <t>38022</t>
         </is>
@@ -17286,7 +17326,7 @@
           <t>YOSHIDA Taku</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr">
+      <c r="X294" t="inlineStr">
         <is>
           <t>41611</t>
         </is>
@@ -17344,7 +17384,7 @@
           <t>MUNSCH Manuel</t>
         </is>
       </c>
-      <c r="U295" t="inlineStr">
+      <c r="X295" t="inlineStr">
         <is>
           <t>35631</t>
         </is>
@@ -17402,7 +17442,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U296" t="inlineStr">
+      <c r="X296" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -17460,7 +17500,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U297" t="inlineStr">
+      <c r="X297" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -17518,7 +17558,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U298" t="inlineStr">
+      <c r="X298" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -17576,7 +17616,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr">
+      <c r="X299" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -17634,7 +17674,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U300" t="inlineStr">
+      <c r="X300" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -17692,7 +17732,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U301" t="inlineStr">
+      <c r="X301" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -17750,7 +17790,7 @@
           <t>NABASKUES Unai</t>
         </is>
       </c>
-      <c r="U302" t="inlineStr">
+      <c r="X302" t="inlineStr">
         <is>
           <t>38775</t>
         </is>
@@ -17808,7 +17848,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U303" t="inlineStr">
+      <c r="X303" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -17866,7 +17906,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U304" t="inlineStr">
+      <c r="X304" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -17924,7 +17964,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U305" t="inlineStr">
+      <c r="X305" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -17982,7 +18022,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U306" t="inlineStr">
+      <c r="X306" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -18040,7 +18080,7 @@
           <t>POWELL Richard</t>
         </is>
       </c>
-      <c r="U307" t="inlineStr">
+      <c r="X307" t="inlineStr">
         <is>
           <t>36444</t>
         </is>
@@ -18098,7 +18138,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U308" t="inlineStr">
+      <c r="X308" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -18209,7 +18249,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U310" t="inlineStr">
+      <c r="X310" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -18267,7 +18307,7 @@
           <t>DAILLE Etienne</t>
         </is>
       </c>
-      <c r="U311" t="inlineStr">
+      <c r="X311" t="inlineStr">
         <is>
           <t>35308</t>
         </is>
@@ -18325,7 +18365,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U312" t="inlineStr">
+      <c r="X312" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -18383,7 +18423,7 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U313" t="inlineStr">
+      <c r="X313" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -18441,7 +18481,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U314" t="inlineStr">
+      <c r="X314" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -18499,7 +18539,7 @@
           <t>HILGERT Lubos</t>
         </is>
       </c>
-      <c r="U315" t="inlineStr">
+      <c r="X315" t="inlineStr">
         <is>
           <t>35032</t>
         </is>
@@ -18557,7 +18597,7 @@
           <t>ALBREHT Martin</t>
         </is>
       </c>
-      <c r="U316" t="inlineStr">
+      <c r="X316" t="inlineStr">
         <is>
           <t>36898</t>
         </is>
@@ -18615,7 +18655,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U317" t="inlineStr">
+      <c r="X317" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -18673,7 +18713,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U318" t="inlineStr">
+      <c r="X318" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -18731,7 +18771,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U319" t="inlineStr">
+      <c r="X319" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -19001,7 +19041,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
+      <c r="X324" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -19059,7 +19099,7 @@
           <t>SANGSUWAN Ravisara</t>
         </is>
       </c>
-      <c r="U325" t="inlineStr">
+      <c r="X325" t="inlineStr">
         <is>
           <t>68858</t>
         </is>
@@ -19117,7 +19157,7 @@
           <t>RAZEGHIAN Roxana</t>
         </is>
       </c>
-      <c r="U326" t="inlineStr">
+      <c r="X326" t="inlineStr">
         <is>
           <t>63124</t>
         </is>
@@ -19175,7 +19215,7 @@
           <t>DUANGLAWA Atcharaporn</t>
         </is>
       </c>
-      <c r="U327" t="inlineStr">
+      <c r="X327" t="inlineStr">
         <is>
           <t>61799</t>
         </is>
@@ -19233,7 +19273,7 @@
           <t>PETROVIC Kristina</t>
         </is>
       </c>
-      <c r="U328" t="inlineStr">
+      <c r="X328" t="inlineStr">
         <is>
           <t>44568</t>
         </is>
@@ -19291,7 +19331,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="X329" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -19349,7 +19389,7 @@
           <t>JODAR Celia</t>
         </is>
       </c>
-      <c r="U330" t="inlineStr">
+      <c r="X330" t="inlineStr">
         <is>
           <t>36936</t>
         </is>
@@ -19407,7 +19447,7 @@
           <t>JAMILI Hind</t>
         </is>
       </c>
-      <c r="U331" t="inlineStr">
+      <c r="X331" t="inlineStr">
         <is>
           <t>43390</t>
         </is>
@@ -19465,7 +19505,7 @@
           <t>CASSINI Maria Luz</t>
         </is>
       </c>
-      <c r="U332" t="inlineStr">
+      <c r="X332" t="inlineStr">
         <is>
           <t>41627</t>
         </is>
@@ -19523,7 +19563,7 @@
           <t>MISHIMA Ren</t>
         </is>
       </c>
-      <c r="U333" t="inlineStr">
+      <c r="X333" t="inlineStr">
         <is>
           <t>37757</t>
         </is>
@@ -19581,7 +19621,7 @@
           <t>CONLAN Aisling</t>
         </is>
       </c>
-      <c r="U334" t="inlineStr">
+      <c r="X334" t="inlineStr">
         <is>
           <t>35814</t>
         </is>
@@ -19639,7 +19679,7 @@
           <t>GRATWOHL Andrea</t>
         </is>
       </c>
-      <c r="U335" t="inlineStr">
+      <c r="X335" t="inlineStr">
         <is>
           <t>35429</t>
         </is>
@@ -19697,7 +19737,7 @@
           <t>HIGGINS Anna</t>
         </is>
       </c>
-      <c r="U336" t="inlineStr">
+      <c r="X336" t="inlineStr">
         <is>
           <t>42107</t>
         </is>
@@ -19861,7 +19901,7 @@
           <t>IFARRAGUERRI Anna Maria</t>
         </is>
       </c>
-      <c r="U339" t="inlineStr">
+      <c r="X339" t="inlineStr">
         <is>
           <t>39209</t>
         </is>
@@ -19919,7 +19959,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U340" t="inlineStr">
+      <c r="X340" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -19977,7 +20017,7 @@
           <t>NICHOLAS Ella</t>
         </is>
       </c>
-      <c r="U341" t="inlineStr">
+      <c r="X341" t="inlineStr">
         <is>
           <t>36591</t>
         </is>
@@ -20035,7 +20075,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U342" t="inlineStr">
+      <c r="X342" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -20146,7 +20186,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U344" t="inlineStr">
+      <c r="X344" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -20204,7 +20244,7 @@
           <t>GROENEVELD Jessica</t>
         </is>
       </c>
-      <c r="U345" t="inlineStr">
+      <c r="X345" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
@@ -20262,7 +20302,7 @@
           <t>NEE Ashley</t>
         </is>
       </c>
-      <c r="U346" t="inlineStr">
+      <c r="X346" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
@@ -20320,7 +20360,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U347" t="inlineStr">
+      <c r="X347" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -20378,7 +20418,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U348" t="inlineStr">
+      <c r="X348" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -20436,7 +20476,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U349" t="inlineStr">
+      <c r="X349" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -20494,7 +20534,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U350" t="inlineStr">
+      <c r="X350" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -20552,7 +20592,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U351" t="inlineStr">
+      <c r="X351" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -20610,7 +20650,7 @@
           <t>MEDON Joanna</t>
         </is>
       </c>
-      <c r="U352" t="inlineStr">
+      <c r="X352" t="inlineStr">
         <is>
           <t>35438</t>
         </is>
@@ -20668,7 +20708,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U353" t="inlineStr">
+      <c r="X353" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -20779,7 +20819,7 @@
           <t>NEVARILOVA Kristina</t>
         </is>
       </c>
-      <c r="U355" t="inlineStr">
+      <c r="X355" t="inlineStr">
         <is>
           <t>35467</t>
         </is>
@@ -20837,7 +20877,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U356" t="inlineStr">
+      <c r="X356" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -20895,7 +20935,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U357" t="inlineStr">
+      <c r="X357" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -20953,7 +20993,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U358" t="inlineStr">
+      <c r="X358" t="inlineStr">
         <is>
           <t>35231</t>
         </is>
@@ -21011,7 +21051,7 @@
           <t>OBLINGER-PETERS Violetta</t>
         </is>
       </c>
-      <c r="U359" t="inlineStr">
+      <c r="X359" t="inlineStr">
         <is>
           <t>35289</t>
         </is>
@@ -21069,7 +21109,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U360" t="inlineStr">
+      <c r="X360" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -21127,7 +21167,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U361" t="inlineStr">
+      <c r="X361" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -21185,7 +21225,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U362" t="inlineStr">
+      <c r="X362" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -21243,7 +21283,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U363" t="inlineStr">
+      <c r="X363" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -21301,7 +21341,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U364" t="inlineStr">
+      <c r="X364" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -21359,7 +21399,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U365" t="inlineStr">
+      <c r="X365" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -21417,7 +21457,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U366" t="inlineStr">
+      <c r="X366" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -21475,7 +21515,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U367" t="inlineStr">
+      <c r="X367" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -21586,7 +21626,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U369" t="inlineStr">
+      <c r="X369" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -21644,7 +21684,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U370" t="inlineStr">
+      <c r="X370" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -21702,7 +21742,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U371" t="inlineStr">
+      <c r="X371" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -21760,7 +21800,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U372" t="inlineStr">
+      <c r="X372" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -21818,7 +21858,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U373" t="inlineStr">
+      <c r="X373" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -21876,7 +21916,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U374" t="inlineStr">
+      <c r="X374" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -21987,7 +22027,7 @@
           <t>FER Emilie</t>
         </is>
       </c>
-      <c r="U376" t="inlineStr">
+      <c r="X376" t="inlineStr">
         <is>
           <t>35314</t>
         </is>
@@ -22045,7 +22085,7 @@
           <t>HILGERTOVA Stepanka</t>
         </is>
       </c>
-      <c r="U377" t="inlineStr">
+      <c r="X377" t="inlineStr">
         <is>
           <t>35035</t>
         </is>
@@ -22103,7 +22143,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U378" t="inlineStr">
+      <c r="X378" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -22161,7 +22201,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U379" t="inlineStr">
+      <c r="X379" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -22219,7 +22259,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U380" t="inlineStr">
+      <c r="X380" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -22277,7 +22317,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U381" t="inlineStr">
+      <c r="X381" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -22335,7 +22375,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U382" t="inlineStr">
+      <c r="X382" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -22451,12 +22491,12 @@
           <t>SEEMANN Eloi</t>
         </is>
       </c>
-      <c r="U384" t="inlineStr">
+      <c r="X384" t="inlineStr">
         <is>
           <t>68753</t>
         </is>
       </c>
-      <c r="V384" t="inlineStr">
+      <c r="Y384" t="inlineStr">
         <is>
           <t>44378</t>
         </is>
@@ -22519,12 +22559,12 @@
           <t>SOSA Angelo</t>
         </is>
       </c>
-      <c r="U385" t="inlineStr">
+      <c r="X385" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
       </c>
-      <c r="V385" t="inlineStr">
+      <c r="Y385" t="inlineStr">
         <is>
           <t>51793</t>
         </is>
@@ -22587,12 +22627,12 @@
           <t>VIEIRA Cassiano</t>
         </is>
       </c>
-      <c r="U386" t="inlineStr">
+      <c r="X386" t="inlineStr">
         <is>
           <t>42977</t>
         </is>
       </c>
-      <c r="V386" t="inlineStr">
+      <c r="Y386" t="inlineStr">
         <is>
           <t>42976</t>
         </is>
@@ -22655,12 +22695,12 @@
           <t>KASPAR Albert</t>
         </is>
       </c>
-      <c r="U387" t="inlineStr">
+      <c r="X387" t="inlineStr">
         <is>
           <t>42012</t>
         </is>
       </c>
-      <c r="V387" t="inlineStr">
+      <c r="Y387" t="inlineStr">
         <is>
           <t>42013</t>
         </is>
@@ -22723,12 +22763,12 @@
           <t>OLIVEIRA Anderson</t>
         </is>
       </c>
-      <c r="U388" t="inlineStr">
+      <c r="X388" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
       </c>
-      <c r="V388" t="inlineStr">
+      <c r="Y388" t="inlineStr">
         <is>
           <t>38020</t>
         </is>
@@ -22791,12 +22831,12 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U389" t="inlineStr">
+      <c r="X389" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
       </c>
-      <c r="V389" t="inlineStr">
+      <c r="Y389" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -22859,12 +22899,12 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U390" t="inlineStr">
+      <c r="X390" t="inlineStr">
         <is>
           <t>35068</t>
         </is>
       </c>
-      <c r="V390" t="inlineStr">
+      <c r="Y390" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -22927,12 +22967,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U391" t="inlineStr">
+      <c r="X391" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V391" t="inlineStr">
+      <c r="Y391" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -22995,12 +23035,12 @@
           <t>USHAKOV Artem</t>
         </is>
       </c>
-      <c r="U392" t="inlineStr">
+      <c r="X392" t="inlineStr">
         <is>
           <t>35454</t>
         </is>
       </c>
-      <c r="V392" t="inlineStr">
+      <c r="Y392" t="inlineStr">
         <is>
           <t>35455</t>
         </is>
@@ -23063,12 +23103,12 @@
           <t>CAILHOL Hugo</t>
         </is>
       </c>
-      <c r="U393" t="inlineStr">
+      <c r="X393" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
       </c>
-      <c r="V393" t="inlineStr">
+      <c r="Y393" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
@@ -23131,12 +23171,12 @@
           <t>FERRARI Niccolo</t>
         </is>
       </c>
-      <c r="U394" t="inlineStr">
+      <c r="X394" t="inlineStr">
         <is>
           <t>35497</t>
         </is>
       </c>
-      <c r="V394" t="inlineStr">
+      <c r="Y394" t="inlineStr">
         <is>
           <t>35498</t>
         </is>
@@ -23199,12 +23239,12 @@
           <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
-      <c r="U395" t="inlineStr">
+      <c r="X395" t="inlineStr">
         <is>
           <t>35356</t>
         </is>
       </c>
-      <c r="V395" t="inlineStr">
+      <c r="Y395" t="inlineStr">
         <is>
           <t>35357</t>
         </is>
@@ -23267,12 +23307,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U396" t="inlineStr">
+      <c r="X396" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V396" t="inlineStr">
+      <c r="Y396" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -23335,12 +23375,12 @@
           <t>PEREZ Jesus</t>
         </is>
       </c>
-      <c r="U397" t="inlineStr">
+      <c r="X397" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
       </c>
-      <c r="V397" t="inlineStr">
+      <c r="Y397" t="inlineStr">
         <is>
           <t>36091</t>
         </is>
@@ -23403,12 +23443,12 @@
           <t>MAJERCZAK Grzegorz</t>
         </is>
       </c>
-      <c r="U398" t="inlineStr">
+      <c r="X398" t="inlineStr">
         <is>
           <t>35085</t>
         </is>
       </c>
-      <c r="V398" t="inlineStr">
+      <c r="Y398" t="inlineStr">
         <is>
           <t>35086</t>
         </is>
@@ -23471,12 +23511,12 @@
           <t>MUELLER Kevin</t>
         </is>
       </c>
-      <c r="U399" t="inlineStr">
+      <c r="X399" t="inlineStr">
         <is>
           <t>35148</t>
         </is>
       </c>
-      <c r="V399" t="inlineStr">
+      <c r="Y399" t="inlineStr">
         <is>
           <t>35149</t>
         </is>
@@ -23539,12 +23579,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U400" t="inlineStr">
+      <c r="X400" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V400" t="inlineStr">
+      <c r="Y400" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -23607,12 +23647,12 @@
           <t>BRZEZINSKI Andrzej</t>
         </is>
       </c>
-      <c r="U401" t="inlineStr">
+      <c r="X401" t="inlineStr">
         <is>
           <t>35082</t>
         </is>
       </c>
-      <c r="V401" t="inlineStr">
+      <c r="Y401" t="inlineStr">
         <is>
           <t>35081</t>
         </is>
@@ -23675,12 +23715,12 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
-      <c r="U402" t="inlineStr">
+      <c r="X402" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
       </c>
-      <c r="V402" t="inlineStr">
+      <c r="Y402" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -23743,12 +23783,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U403" t="inlineStr">
+      <c r="X403" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V403" t="inlineStr">
+      <c r="Y403" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -23811,12 +23851,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U404" t="inlineStr">
+      <c r="X404" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V404" t="inlineStr">
+      <c r="Y404" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -23879,12 +23919,12 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U405" t="inlineStr">
+      <c r="X405" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
       </c>
-      <c r="V405" t="inlineStr">
+      <c r="Y405" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -23947,12 +23987,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U406" t="inlineStr">
+      <c r="X406" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V406" t="inlineStr">
+      <c r="Y406" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -24015,12 +24055,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U407" t="inlineStr">
+      <c r="X407" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V407" t="inlineStr">
+      <c r="Y407" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -24083,12 +24123,12 @@
           <t>TALJAT Saso</t>
         </is>
       </c>
-      <c r="U408" t="inlineStr">
+      <c r="X408" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
       </c>
-      <c r="V408" t="inlineStr">
+      <c r="Y408" t="inlineStr">
         <is>
           <t>36270</t>
         </is>
@@ -24151,12 +24191,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U409" t="inlineStr">
+      <c r="X409" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V409" t="inlineStr">
+      <c r="Y409" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -24214,7 +24254,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U410" t="inlineStr">
+      <c r="X410" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -24272,7 +24312,7 @@
           <t>SANGSUWAN Ravisara</t>
         </is>
       </c>
-      <c r="U411" t="inlineStr">
+      <c r="X411" t="inlineStr">
         <is>
           <t>68858</t>
         </is>
@@ -24330,7 +24370,7 @@
           <t>RAZEGHIAN Roxana</t>
         </is>
       </c>
-      <c r="U412" t="inlineStr">
+      <c r="X412" t="inlineStr">
         <is>
           <t>63124</t>
         </is>
@@ -24388,7 +24428,7 @@
           <t>DUANGLAWA Atcharaporn</t>
         </is>
       </c>
-      <c r="U413" t="inlineStr">
+      <c r="X413" t="inlineStr">
         <is>
           <t>61799</t>
         </is>
@@ -24446,7 +24486,7 @@
           <t>PETROVIC Kristina</t>
         </is>
       </c>
-      <c r="U414" t="inlineStr">
+      <c r="X414" t="inlineStr">
         <is>
           <t>44568</t>
         </is>
@@ -24504,7 +24544,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U415" t="inlineStr">
+      <c r="X415" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -24562,7 +24602,7 @@
           <t>JODAR Celia</t>
         </is>
       </c>
-      <c r="U416" t="inlineStr">
+      <c r="X416" t="inlineStr">
         <is>
           <t>36936</t>
         </is>
@@ -24620,7 +24660,7 @@
           <t>JAMILI Hind</t>
         </is>
       </c>
-      <c r="U417" t="inlineStr">
+      <c r="X417" t="inlineStr">
         <is>
           <t>43390</t>
         </is>
@@ -24678,7 +24718,7 @@
           <t>CASSINI Maria Luz</t>
         </is>
       </c>
-      <c r="U418" t="inlineStr">
+      <c r="X418" t="inlineStr">
         <is>
           <t>41627</t>
         </is>
@@ -24736,7 +24776,7 @@
           <t>MISHIMA Ren</t>
         </is>
       </c>
-      <c r="U419" t="inlineStr">
+      <c r="X419" t="inlineStr">
         <is>
           <t>37757</t>
         </is>
@@ -24794,7 +24834,7 @@
           <t>CONLAN Aisling</t>
         </is>
       </c>
-      <c r="U420" t="inlineStr">
+      <c r="X420" t="inlineStr">
         <is>
           <t>35814</t>
         </is>
@@ -24852,7 +24892,7 @@
           <t>GRATWOHL Andrea</t>
         </is>
       </c>
-      <c r="U421" t="inlineStr">
+      <c r="X421" t="inlineStr">
         <is>
           <t>35429</t>
         </is>
@@ -24910,7 +24950,7 @@
           <t>HIGGINS Anna</t>
         </is>
       </c>
-      <c r="U422" t="inlineStr">
+      <c r="X422" t="inlineStr">
         <is>
           <t>42107</t>
         </is>
@@ -25074,7 +25114,7 @@
           <t>IFARRAGUERRI Anna Maria</t>
         </is>
       </c>
-      <c r="U425" t="inlineStr">
+      <c r="X425" t="inlineStr">
         <is>
           <t>39209</t>
         </is>
@@ -25132,7 +25172,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U426" t="inlineStr">
+      <c r="X426" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -25190,7 +25230,7 @@
           <t>NICHOLAS Ella</t>
         </is>
       </c>
-      <c r="U427" t="inlineStr">
+      <c r="X427" t="inlineStr">
         <is>
           <t>36591</t>
         </is>
@@ -25248,7 +25288,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U428" t="inlineStr">
+      <c r="X428" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -25359,7 +25399,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U430" t="inlineStr">
+      <c r="X430" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -25417,7 +25457,7 @@
           <t>GROENEVELD Jessica</t>
         </is>
       </c>
-      <c r="U431" t="inlineStr">
+      <c r="X431" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
@@ -25475,7 +25515,7 @@
           <t>NEE Ashley</t>
         </is>
       </c>
-      <c r="U432" t="inlineStr">
+      <c r="X432" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
@@ -25533,7 +25573,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U433" t="inlineStr">
+      <c r="X433" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -25591,7 +25631,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U434" t="inlineStr">
+      <c r="X434" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -25649,7 +25689,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U435" t="inlineStr">
+      <c r="X435" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -25707,7 +25747,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U436" t="inlineStr">
+      <c r="X436" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -25765,7 +25805,7 @@
           <t>MEDON Joanna</t>
         </is>
       </c>
-      <c r="U437" t="inlineStr">
+      <c r="X437" t="inlineStr">
         <is>
           <t>35438</t>
         </is>
@@ -25823,7 +25863,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U438" t="inlineStr">
+      <c r="X438" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -25881,7 +25921,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U439" t="inlineStr">
+      <c r="X439" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -25939,7 +25979,7 @@
           <t>OBLINGER-PETERS Violetta</t>
         </is>
       </c>
-      <c r="U440" t="inlineStr">
+      <c r="X440" t="inlineStr">
         <is>
           <t>35289</t>
         </is>
@@ -25997,7 +26037,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U441" t="inlineStr">
+      <c r="X441" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -26055,7 +26095,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U442" t="inlineStr">
+      <c r="X442" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -26113,7 +26153,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U443" t="inlineStr">
+      <c r="X443" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -26171,7 +26211,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U444" t="inlineStr">
+      <c r="X444" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -26229,7 +26269,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U445" t="inlineStr">
+      <c r="X445" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -26287,7 +26327,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U446" t="inlineStr">
+      <c r="X446" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -26345,7 +26385,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U447" t="inlineStr">
+      <c r="X447" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -26403,7 +26443,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U448" t="inlineStr">
+      <c r="X448" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -26461,7 +26501,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U449" t="inlineStr">
+      <c r="X449" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -26519,7 +26559,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U450" t="inlineStr">
+      <c r="X450" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -26582,12 +26622,12 @@
           <t>SEEMANN Eloi</t>
         </is>
       </c>
-      <c r="U451" t="inlineStr">
+      <c r="X451" t="inlineStr">
         <is>
           <t>68753</t>
         </is>
       </c>
-      <c r="V451" t="inlineStr">
+      <c r="Y451" t="inlineStr">
         <is>
           <t>44378</t>
         </is>
@@ -26650,12 +26690,12 @@
           <t>SOSA Angelo</t>
         </is>
       </c>
-      <c r="U452" t="inlineStr">
+      <c r="X452" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
       </c>
-      <c r="V452" t="inlineStr">
+      <c r="Y452" t="inlineStr">
         <is>
           <t>51793</t>
         </is>
@@ -26718,12 +26758,12 @@
           <t>VIEIRA Cassiano</t>
         </is>
       </c>
-      <c r="U453" t="inlineStr">
+      <c r="X453" t="inlineStr">
         <is>
           <t>42977</t>
         </is>
       </c>
-      <c r="V453" t="inlineStr">
+      <c r="Y453" t="inlineStr">
         <is>
           <t>42976</t>
         </is>
@@ -26786,12 +26826,12 @@
           <t>KASPAR Albert</t>
         </is>
       </c>
-      <c r="U454" t="inlineStr">
+      <c r="X454" t="inlineStr">
         <is>
           <t>42012</t>
         </is>
       </c>
-      <c r="V454" t="inlineStr">
+      <c r="Y454" t="inlineStr">
         <is>
           <t>42013</t>
         </is>
@@ -26854,12 +26894,12 @@
           <t>OLIVEIRA Anderson</t>
         </is>
       </c>
-      <c r="U455" t="inlineStr">
+      <c r="X455" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
       </c>
-      <c r="V455" t="inlineStr">
+      <c r="Y455" t="inlineStr">
         <is>
           <t>38020</t>
         </is>
@@ -26922,12 +26962,12 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U456" t="inlineStr">
+      <c r="X456" t="inlineStr">
         <is>
           <t>35068</t>
         </is>
       </c>
-      <c r="V456" t="inlineStr">
+      <c r="Y456" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -26990,12 +27030,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U457" t="inlineStr">
+      <c r="X457" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V457" t="inlineStr">
+      <c r="Y457" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -27058,12 +27098,12 @@
           <t>USHAKOV Artem</t>
         </is>
       </c>
-      <c r="U458" t="inlineStr">
+      <c r="X458" t="inlineStr">
         <is>
           <t>35454</t>
         </is>
       </c>
-      <c r="V458" t="inlineStr">
+      <c r="Y458" t="inlineStr">
         <is>
           <t>35455</t>
         </is>
@@ -27126,12 +27166,12 @@
           <t>FERRARI Niccolo</t>
         </is>
       </c>
-      <c r="U459" t="inlineStr">
+      <c r="X459" t="inlineStr">
         <is>
           <t>35497</t>
         </is>
       </c>
-      <c r="V459" t="inlineStr">
+      <c r="Y459" t="inlineStr">
         <is>
           <t>35498</t>
         </is>
@@ -27194,12 +27234,12 @@
           <t>PEREZ Jesus</t>
         </is>
       </c>
-      <c r="U460" t="inlineStr">
+      <c r="X460" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
       </c>
-      <c r="V460" t="inlineStr">
+      <c r="Y460" t="inlineStr">
         <is>
           <t>36091</t>
         </is>
@@ -27262,12 +27302,12 @@
           <t>BRZEZINSKI Andrzej</t>
         </is>
       </c>
-      <c r="U461" t="inlineStr">
+      <c r="X461" t="inlineStr">
         <is>
           <t>35082</t>
         </is>
       </c>
-      <c r="V461" t="inlineStr">
+      <c r="Y461" t="inlineStr">
         <is>
           <t>35081</t>
         </is>
@@ -27643,7 +27683,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U468" t="inlineStr">
+      <c r="X468" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -27701,7 +27741,7 @@
           <t>ERGUIN Jon</t>
         </is>
       </c>
-      <c r="U469" t="inlineStr">
+      <c r="X469" t="inlineStr">
         <is>
           <t>35740</t>
         </is>
@@ -27759,7 +27799,7 @@
           <t>CURCEL Leonardo</t>
         </is>
       </c>
-      <c r="U470" t="inlineStr">
+      <c r="X470" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
@@ -27817,7 +27857,7 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U471" t="inlineStr">
+      <c r="X471" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -27875,7 +27915,7 @@
           <t>MIRGORODSKY Marko</t>
         </is>
       </c>
-      <c r="U472" t="inlineStr">
+      <c r="X472" t="inlineStr">
         <is>
           <t>42019</t>
         </is>
@@ -27933,7 +27973,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U473" t="inlineStr">
+      <c r="X473" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -27991,7 +28031,7 @@
           <t>COF Blaz</t>
         </is>
       </c>
-      <c r="U474" t="inlineStr">
+      <c r="X474" t="inlineStr">
         <is>
           <t>36897</t>
         </is>
@@ -28049,7 +28089,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U475" t="inlineStr">
+      <c r="X475" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -28160,7 +28200,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U477" t="inlineStr">
+      <c r="X477" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -28218,7 +28258,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U478" t="inlineStr">
+      <c r="X478" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -28276,7 +28316,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U479" t="inlineStr">
+      <c r="X479" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -28334,7 +28374,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U480" t="inlineStr">
+      <c r="X480" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -28392,7 +28432,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U481" t="inlineStr">
+      <c r="X481" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -28450,7 +28490,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U482" t="inlineStr">
+      <c r="X482" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -28508,7 +28548,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U483" t="inlineStr">
+      <c r="X483" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -28566,7 +28606,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U484" t="inlineStr">
+      <c r="X484" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -28624,7 +28664,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U485" t="inlineStr">
+      <c r="X485" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -28682,7 +28722,7 @@
           <t>TILLARD Pierre-Antoine</t>
         </is>
       </c>
-      <c r="U486" t="inlineStr">
+      <c r="X486" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
@@ -28740,7 +28780,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U487" t="inlineStr">
+      <c r="X487" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -28798,7 +28838,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U488" t="inlineStr">
+      <c r="X488" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -28856,7 +28896,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U489" t="inlineStr">
+      <c r="X489" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -28914,7 +28954,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U490" t="inlineStr">
+      <c r="X490" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -28972,7 +29012,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U491" t="inlineStr">
+      <c r="X491" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -29030,7 +29070,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U492" t="inlineStr">
+      <c r="X492" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -29088,7 +29128,7 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U493" t="inlineStr">
+      <c r="X493" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -29146,7 +29186,7 @@
           <t>PESCHIER Nicolas</t>
         </is>
       </c>
-      <c r="U494" t="inlineStr">
+      <c r="X494" t="inlineStr">
         <is>
           <t>35401</t>
         </is>
@@ -29204,7 +29244,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U495" t="inlineStr">
+      <c r="X495" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -29262,7 +29302,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U496" t="inlineStr">
+      <c r="X496" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -29320,7 +29360,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U497" t="inlineStr">
+      <c r="X497" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -29378,7 +29418,7 @@
           <t>CHEN Wei-Han</t>
         </is>
       </c>
-      <c r="U498" t="inlineStr">
+      <c r="X498" t="inlineStr">
         <is>
           <t>61630</t>
         </is>
@@ -29436,7 +29476,7 @@
           <t>GLEJTEKOVA Simona</t>
         </is>
       </c>
-      <c r="U499" t="inlineStr">
+      <c r="X499" t="inlineStr">
         <is>
           <t>55166</t>
         </is>
@@ -29494,7 +29534,7 @@
           <t>BORROWS Alison</t>
         </is>
       </c>
-      <c r="U500" t="inlineStr">
+      <c r="X500" t="inlineStr">
         <is>
           <t>38440</t>
         </is>
@@ -29605,7 +29645,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U502" t="inlineStr">
+      <c r="X502" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -29663,7 +29703,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U503" t="inlineStr">
+      <c r="X503" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -29721,7 +29761,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U504" t="inlineStr">
+      <c r="X504" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -29779,7 +29819,7 @@
           <t>NAVEAU Laurine</t>
         </is>
       </c>
-      <c r="U505" t="inlineStr">
+      <c r="X505" t="inlineStr">
         <is>
           <t>53246</t>
         </is>
@@ -29890,7 +29930,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U507" t="inlineStr">
+      <c r="X507" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -29948,7 +29988,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U508" t="inlineStr">
+      <c r="X508" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -30059,7 +30099,7 @@
           <t>GIBSON Eilidh</t>
         </is>
       </c>
-      <c r="U510" t="inlineStr">
+      <c r="X510" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
@@ -30117,7 +30157,7 @@
           <t>SATKOVA Martina</t>
         </is>
       </c>
-      <c r="U511" t="inlineStr">
+      <c r="X511" t="inlineStr">
         <is>
           <t>42008</t>
         </is>
@@ -30175,7 +30215,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U512" t="inlineStr">
+      <c r="X512" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -30286,7 +30326,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U514" t="inlineStr">
+      <c r="X514" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -30397,7 +30437,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U516" t="inlineStr">
+      <c r="X516" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -30455,7 +30495,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U517" t="inlineStr">
+      <c r="X517" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -30513,7 +30553,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U518" t="inlineStr">
+      <c r="X518" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -30571,7 +30611,7 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U519" t="inlineStr">
+      <c r="X519" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -30629,7 +30669,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U520" t="inlineStr">
+      <c r="X520" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -30687,7 +30727,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U521" t="inlineStr">
+      <c r="X521" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -30745,7 +30785,7 @@
           <t>POWELL Richard</t>
         </is>
       </c>
-      <c r="U522" t="inlineStr">
+      <c r="X522" t="inlineStr">
         <is>
           <t>36444</t>
         </is>
@@ -30803,7 +30843,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U523" t="inlineStr">
+      <c r="X523" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -30861,7 +30901,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U524" t="inlineStr">
+      <c r="X524" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -30919,7 +30959,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U525" t="inlineStr">
+      <c r="X525" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -30977,7 +31017,7 @@
           <t>HILGERT Lubos</t>
         </is>
       </c>
-      <c r="U526" t="inlineStr">
+      <c r="X526" t="inlineStr">
         <is>
           <t>35032</t>
         </is>
@@ -31035,7 +31075,7 @@
           <t>DAILLE Etienne</t>
         </is>
       </c>
-      <c r="U527" t="inlineStr">
+      <c r="X527" t="inlineStr">
         <is>
           <t>35308</t>
         </is>
@@ -31093,7 +31133,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U528" t="inlineStr">
+      <c r="X528" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -31151,7 +31191,7 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U529" t="inlineStr">
+      <c r="X529" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -31209,7 +31249,7 @@
           <t>PETERLIN Janos</t>
         </is>
       </c>
-      <c r="U530" t="inlineStr">
+      <c r="X530" t="inlineStr">
         <is>
           <t>36268</t>
         </is>
@@ -31267,7 +31307,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U531" t="inlineStr">
+      <c r="X531" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -31325,7 +31365,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U532" t="inlineStr">
+      <c r="X532" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -31383,7 +31423,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U533" t="inlineStr">
+      <c r="X533" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -31441,7 +31481,7 @@
           <t>MOLMENTI Daniele</t>
         </is>
       </c>
-      <c r="U534" t="inlineStr">
+      <c r="X534" t="inlineStr">
         <is>
           <t>42017</t>
         </is>
@@ -31499,7 +31539,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U535" t="inlineStr">
+      <c r="X535" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -31557,7 +31597,7 @@
           <t>TRAVOSTINO Benjamin</t>
         </is>
       </c>
-      <c r="U536" t="inlineStr">
+      <c r="X536" t="inlineStr">
         <is>
           <t>68795</t>
         </is>
@@ -31615,7 +31655,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U537" t="inlineStr">
+      <c r="X537" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -31673,7 +31713,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U538" t="inlineStr">
+      <c r="X538" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -31784,7 +31824,7 @@
           <t>MEGLIC Jure</t>
         </is>
       </c>
-      <c r="U540" t="inlineStr">
+      <c r="X540" t="inlineStr">
         <is>
           <t>35590</t>
         </is>
@@ -31842,7 +31882,7 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U541" t="inlineStr">
+      <c r="X541" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -31900,7 +31940,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U542" t="inlineStr">
+      <c r="X542" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -31958,7 +31998,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U543" t="inlineStr">
+      <c r="X543" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -32016,7 +32056,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U544" t="inlineStr">
+      <c r="X544" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -32074,7 +32114,7 @@
           <t>ROMEO Andrea</t>
         </is>
       </c>
-      <c r="U545" t="inlineStr">
+      <c r="X545" t="inlineStr">
         <is>
           <t>35502</t>
         </is>
@@ -32132,7 +32172,7 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U546" t="inlineStr">
+      <c r="X546" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -32190,7 +32230,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U547" t="inlineStr">
+      <c r="X547" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -32248,7 +32288,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U548" t="inlineStr">
+      <c r="X548" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -32306,7 +32346,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U549" t="inlineStr">
+      <c r="X549" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -32364,7 +32404,7 @@
           <t>BOECKELMANN Paul</t>
         </is>
       </c>
-      <c r="U550" t="inlineStr">
+      <c r="X550" t="inlineStr">
         <is>
           <t>35118</t>
         </is>
@@ -32422,7 +32462,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U551" t="inlineStr">
+      <c r="X551" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -32533,7 +32573,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U553" t="inlineStr">
+      <c r="X553" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -32591,7 +32631,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U554" t="inlineStr">
+      <c r="X554" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -32649,7 +32689,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U555" t="inlineStr">
+      <c r="X555" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -32707,7 +32747,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U556" t="inlineStr">
+      <c r="X556" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -32765,7 +32805,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U557" t="inlineStr">
+      <c r="X557" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -32833,7 +32873,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U558" t="inlineStr">
+      <c r="X558" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -32901,7 +32941,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U559" t="inlineStr">
+      <c r="X559" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -32969,7 +33009,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U560" t="inlineStr">
+      <c r="X560" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -33037,7 +33077,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U561" t="inlineStr">
+      <c r="X561" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -33105,7 +33145,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U562" t="inlineStr">
+      <c r="X562" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -33173,7 +33213,7 @@
           <t>PESCHIER Nicolas</t>
         </is>
       </c>
-      <c r="U563" t="inlineStr">
+      <c r="X563" t="inlineStr">
         <is>
           <t>35401</t>
         </is>
@@ -33241,7 +33281,7 @@
           <t>TILLARD Pierre-Antoine</t>
         </is>
       </c>
-      <c r="U564" t="inlineStr">
+      <c r="X564" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
@@ -33309,7 +33349,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U565" t="inlineStr">
+      <c r="X565" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -33377,7 +33417,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U566" t="inlineStr">
+      <c r="X566" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -33445,7 +33485,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U567" t="inlineStr">
+      <c r="X567" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -33576,7 +33616,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U569" t="inlineStr">
+      <c r="X569" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -33644,7 +33684,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U570" t="inlineStr">
+      <c r="X570" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -33712,7 +33752,7 @@
           <t>SATKOVA Martina</t>
         </is>
       </c>
-      <c r="U571" t="inlineStr">
+      <c r="X571" t="inlineStr">
         <is>
           <t>42008</t>
         </is>
@@ -33780,7 +33820,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U572" t="inlineStr">
+      <c r="X572" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -33848,7 +33888,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U573" t="inlineStr">
+      <c r="X573" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -33979,7 +34019,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U575" t="inlineStr">
+      <c r="X575" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -34110,7 +34150,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U577" t="inlineStr">
+      <c r="X577" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -34178,7 +34218,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U578" t="inlineStr">
+      <c r="X578" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -34246,7 +34286,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U579" t="inlineStr">
+      <c r="X579" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -34314,7 +34354,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U580" t="inlineStr">
+      <c r="X580" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -34382,7 +34422,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U581" t="inlineStr">
+      <c r="X581" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -34450,7 +34490,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U582" t="inlineStr">
+      <c r="X582" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -34518,7 +34558,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U583" t="inlineStr">
+      <c r="X583" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -34586,7 +34626,7 @@
           <t>DAILLE Etienne</t>
         </is>
       </c>
-      <c r="U584" t="inlineStr">
+      <c r="X584" t="inlineStr">
         <is>
           <t>35308</t>
         </is>
@@ -34654,7 +34694,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U585" t="inlineStr">
+      <c r="X585" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -34722,7 +34762,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U586" t="inlineStr">
+      <c r="X586" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -34790,7 +34830,7 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U587" t="inlineStr">
+      <c r="X587" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -35060,7 +35100,7 @@
           <t>NEE Ashley</t>
         </is>
       </c>
-      <c r="U592" t="inlineStr">
+      <c r="X592" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
@@ -35118,7 +35158,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U593" t="inlineStr">
+      <c r="X593" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -35176,7 +35216,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U594" t="inlineStr">
+      <c r="X594" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -35234,7 +35274,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U595" t="inlineStr">
+      <c r="X595" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -35292,7 +35332,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U596" t="inlineStr">
+      <c r="X596" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -35350,7 +35390,7 @@
           <t>OBLINGER-PETERS Violetta</t>
         </is>
       </c>
-      <c r="U597" t="inlineStr">
+      <c r="X597" t="inlineStr">
         <is>
           <t>35289</t>
         </is>
@@ -35408,7 +35448,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U598" t="inlineStr">
+      <c r="X598" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -35466,7 +35506,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U599" t="inlineStr">
+      <c r="X599" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -35524,7 +35564,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U600" t="inlineStr">
+      <c r="X600" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -35582,7 +35622,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U601" t="inlineStr">
+      <c r="X601" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -35640,7 +35680,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U602" t="inlineStr">
+      <c r="X602" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -35698,7 +35738,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U603" t="inlineStr">
+      <c r="X603" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -35756,7 +35796,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U604" t="inlineStr">
+      <c r="X604" t="inlineStr">
         <is>
           <t>35231</t>
         </is>
@@ -35814,7 +35854,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U605" t="inlineStr">
+      <c r="X605" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -35872,7 +35912,7 @@
           <t>HILGERTOVA Stepanka</t>
         </is>
       </c>
-      <c r="U606" t="inlineStr">
+      <c r="X606" t="inlineStr">
         <is>
           <t>35035</t>
         </is>
@@ -35930,7 +35970,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U607" t="inlineStr">
+      <c r="X607" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -35988,7 +36028,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U608" t="inlineStr">
+      <c r="X608" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -36046,7 +36086,7 @@
           <t>NEVARILOVA Kristina</t>
         </is>
       </c>
-      <c r="U609" t="inlineStr">
+      <c r="X609" t="inlineStr">
         <is>
           <t>35467</t>
         </is>
@@ -36157,7 +36197,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U611" t="inlineStr">
+      <c r="X611" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -36215,7 +36255,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U612" t="inlineStr">
+      <c r="X612" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -36273,7 +36313,7 @@
           <t>FER Emilie</t>
         </is>
       </c>
-      <c r="U613" t="inlineStr">
+      <c r="X613" t="inlineStr">
         <is>
           <t>35314</t>
         </is>
@@ -36384,7 +36424,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U615" t="inlineStr">
+      <c r="X615" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -36442,7 +36482,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U616" t="inlineStr">
+      <c r="X616" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -36500,7 +36540,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U617" t="inlineStr">
+      <c r="X617" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -36664,7 +36704,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U620" t="inlineStr">
+      <c r="X620" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -36722,7 +36762,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U621" t="inlineStr">
+      <c r="X621" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -36785,12 +36825,12 @@
           <t>OLIVEIRA Anderson</t>
         </is>
       </c>
-      <c r="U622" t="inlineStr">
+      <c r="X622" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
       </c>
-      <c r="V622" t="inlineStr">
+      <c r="Y622" t="inlineStr">
         <is>
           <t>38020</t>
         </is>
@@ -36853,12 +36893,12 @@
           <t>BRZEZINSKI Andrzej</t>
         </is>
       </c>
-      <c r="U623" t="inlineStr">
+      <c r="X623" t="inlineStr">
         <is>
           <t>35082</t>
         </is>
       </c>
-      <c r="V623" t="inlineStr">
+      <c r="Y623" t="inlineStr">
         <is>
           <t>35081</t>
         </is>
@@ -36921,12 +36961,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U624" t="inlineStr">
+      <c r="X624" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V624" t="inlineStr">
+      <c r="Y624" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -36989,12 +37029,12 @@
           <t>PEREZ Jesus</t>
         </is>
       </c>
-      <c r="U625" t="inlineStr">
+      <c r="X625" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
       </c>
-      <c r="V625" t="inlineStr">
+      <c r="Y625" t="inlineStr">
         <is>
           <t>36091</t>
         </is>
@@ -37057,12 +37097,12 @@
           <t>FERRARI Niccolo</t>
         </is>
       </c>
-      <c r="U626" t="inlineStr">
+      <c r="X626" t="inlineStr">
         <is>
           <t>35497</t>
         </is>
       </c>
-      <c r="V626" t="inlineStr">
+      <c r="Y626" t="inlineStr">
         <is>
           <t>35498</t>
         </is>
@@ -37125,12 +37165,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U627" t="inlineStr">
+      <c r="X627" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V627" t="inlineStr">
+      <c r="Y627" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -37193,12 +37233,12 @@
           <t>CAILHOL Hugo</t>
         </is>
       </c>
-      <c r="U628" t="inlineStr">
+      <c r="X628" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
       </c>
-      <c r="V628" t="inlineStr">
+      <c r="Y628" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
@@ -37261,12 +37301,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U629" t="inlineStr">
+      <c r="X629" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V629" t="inlineStr">
+      <c r="Y629" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -37329,12 +37369,12 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
-      <c r="U630" t="inlineStr">
+      <c r="X630" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
       </c>
-      <c r="V630" t="inlineStr">
+      <c r="Y630" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -37397,12 +37437,12 @@
           <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
-      <c r="U631" t="inlineStr">
+      <c r="X631" t="inlineStr">
         <is>
           <t>35356</t>
         </is>
       </c>
-      <c r="V631" t="inlineStr">
+      <c r="Y631" t="inlineStr">
         <is>
           <t>35357</t>
         </is>
@@ -37465,12 +37505,12 @@
           <t>TALJAT Saso</t>
         </is>
       </c>
-      <c r="U632" t="inlineStr">
+      <c r="X632" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
       </c>
-      <c r="V632" t="inlineStr">
+      <c r="Y632" t="inlineStr">
         <is>
           <t>36270</t>
         </is>
@@ -37533,12 +37573,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U633" t="inlineStr">
+      <c r="X633" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V633" t="inlineStr">
+      <c r="Y633" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -37601,12 +37641,12 @@
           <t>MAJERCZAK Grzegorz</t>
         </is>
       </c>
-      <c r="U634" t="inlineStr">
+      <c r="X634" t="inlineStr">
         <is>
           <t>35085</t>
         </is>
       </c>
-      <c r="V634" t="inlineStr">
+      <c r="Y634" t="inlineStr">
         <is>
           <t>35086</t>
         </is>
@@ -37669,12 +37709,12 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U635" t="inlineStr">
+      <c r="X635" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
       </c>
-      <c r="V635" t="inlineStr">
+      <c r="Y635" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -37737,12 +37777,12 @@
           <t>MUELLER Kevin</t>
         </is>
       </c>
-      <c r="U636" t="inlineStr">
+      <c r="X636" t="inlineStr">
         <is>
           <t>35148</t>
         </is>
       </c>
-      <c r="V636" t="inlineStr">
+      <c r="Y636" t="inlineStr">
         <is>
           <t>35149</t>
         </is>
@@ -37805,12 +37845,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U637" t="inlineStr">
+      <c r="X637" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V637" t="inlineStr">
+      <c r="Y637" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -37873,12 +37913,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U638" t="inlineStr">
+      <c r="X638" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V638" t="inlineStr">
+      <c r="Y638" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -37941,12 +37981,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U639" t="inlineStr">
+      <c r="X639" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V639" t="inlineStr">
+      <c r="Y639" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -38009,12 +38049,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U640" t="inlineStr">
+      <c r="X640" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V640" t="inlineStr">
+      <c r="Y640" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -38077,12 +38117,12 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U641" t="inlineStr">
+      <c r="X641" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
       </c>
-      <c r="V641" t="inlineStr">
+      <c r="Y641" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -38213,7 +38253,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U643" t="inlineStr">
+      <c r="X643" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -38281,7 +38321,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U644" t="inlineStr">
+      <c r="X644" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -38349,7 +38389,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U645" t="inlineStr">
+      <c r="X645" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -38417,7 +38457,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U646" t="inlineStr">
+      <c r="X646" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -38485,7 +38525,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U647" t="inlineStr">
+      <c r="X647" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -38553,7 +38593,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U648" t="inlineStr">
+      <c r="X648" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -38621,7 +38661,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U649" t="inlineStr">
+      <c r="X649" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -38752,7 +38792,7 @@
           <t>OBLINGER-PETERS Violetta</t>
         </is>
       </c>
-      <c r="U651" t="inlineStr">
+      <c r="X651" t="inlineStr">
         <is>
           <t>35289</t>
         </is>
@@ -38825,12 +38865,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U652" t="inlineStr">
+      <c r="X652" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V652" t="inlineStr">
+      <c r="Y652" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -38903,12 +38943,12 @@
           <t>MUELLER Kevin</t>
         </is>
       </c>
-      <c r="U653" t="inlineStr">
+      <c r="X653" t="inlineStr">
         <is>
           <t>35148</t>
         </is>
       </c>
-      <c r="V653" t="inlineStr">
+      <c r="Y653" t="inlineStr">
         <is>
           <t>35149</t>
         </is>
@@ -38981,12 +39021,12 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U654" t="inlineStr">
+      <c r="X654" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
       </c>
-      <c r="V654" t="inlineStr">
+      <c r="Y654" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -39059,12 +39099,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U655" t="inlineStr">
+      <c r="X655" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V655" t="inlineStr">
+      <c r="Y655" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -39137,12 +39177,12 @@
           <t>TALJAT Saso</t>
         </is>
       </c>
-      <c r="U656" t="inlineStr">
+      <c r="X656" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
       </c>
-      <c r="V656" t="inlineStr">
+      <c r="Y656" t="inlineStr">
         <is>
           <t>36270</t>
         </is>
@@ -39215,12 +39255,12 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
-      <c r="U657" t="inlineStr">
+      <c r="X657" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
       </c>
-      <c r="V657" t="inlineStr">
+      <c r="Y657" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -39293,12 +39333,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U658" t="inlineStr">
+      <c r="X658" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V658" t="inlineStr">
+      <c r="Y658" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -39371,12 +39411,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U659" t="inlineStr">
+      <c r="X659" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V659" t="inlineStr">
+      <c r="Y659" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -39449,12 +39489,12 @@
           <t>CAILHOL Hugo</t>
         </is>
       </c>
-      <c r="U660" t="inlineStr">
+      <c r="X660" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
       </c>
-      <c r="V660" t="inlineStr">
+      <c r="Y660" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
@@ -39527,12 +39567,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U661" t="inlineStr">
+      <c r="X661" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V661" t="inlineStr">
+      <c r="Y661" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
